--- a/dpr_dummy.xlsx
+++ b/dpr_dummy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0A78AC9-DF8B-479A-854C-DEECEC9A6F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D1BAB95-D2DF-44AC-AE85-7A69B029BDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{7946C922-F761-4FF1-8407-99021E3A2070}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{1AB92B17-2BEC-47DC-8530-EB04EDF03A72}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 16:24:41</t>
+    <t>Report Generated On: 05.MAY.2026 At 16:42:02</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FE6B-40D9-BCDF-0A9CD6635178}"/>
+              <c16:uniqueId val="{00000000-6C44-49E6-926A-1E99E4AA02FD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FE6B-40D9-BCDF-0A9CD6635178}"/>
+              <c16:uniqueId val="{00000001-6C44-49E6-926A-1E99E4AA02FD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="946656064"/>
-        <c:axId val="946676224"/>
+        <c:axId val="172966047"/>
+        <c:axId val="172955007"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="946656064"/>
+        <c:axId val="172966047"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="946676224"/>
+        <c:crossAx val="172955007"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="946676224"/>
+        <c:axId val="172955007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="946656064"/>
+        <c:crossAx val="172966047"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1269,7 +1269,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5A5F7B5-3734-CABD-9A0B-2B1DF47CF5C8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CAF57CF-A70D-9CE7-BBD3-260C39A94A5E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B1EB3BC-F10B-67FD-9DDB-DB157B500DF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6FD010-F2F2-33BF-E744-A24D43FC7DF7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1303934-391B-45DE-86B3-4E552B10429B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0BD5CC-5A6E-4066-8157-6C7D7DB3F6A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6262,91 +6262,91 @@
         <v>51</v>
       </c>
       <c r="C58" s="73">
-        <v>0.53116243950249997</v>
+        <v>17033.331630000001</v>
       </c>
       <c r="D58" s="73">
-        <v>0.51802865712190005</v>
+        <v>11355.55442</v>
       </c>
       <c r="E58" s="73">
         <v>0</v>
       </c>
       <c r="F58" s="73">
-        <v>0.319923941002</v>
+        <v>18459.998154000001</v>
       </c>
       <c r="G58" s="73">
-        <v>0.34495581952339999</v>
+        <v>8516.6658150000003</v>
       </c>
       <c r="H58" s="73">
-        <v>0.1635629999988</v>
+        <v>22711.108840000001</v>
       </c>
       <c r="I58" s="73">
-        <v>18.088745599999999</v>
+        <v>12977.77648</v>
       </c>
       <c r="J58" s="73">
-        <v>2.8107466400002998</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="K58" s="73">
-        <v>1.6813375540005999</v>
+        <v>3176.6663490000001</v>
       </c>
       <c r="L58" s="73">
-        <v>0</v>
+        <v>3244.4441200000001</v>
       </c>
       <c r="M58" s="73">
-        <v>0.59685871851969996</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="N58" s="73">
-        <v>1.6153345779900002E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="O58" s="73">
-        <v>4.3063639999699997E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="P58" s="73">
         <v>25.114539355448802</v>
       </c>
       <c r="Q58" s="73">
-        <v>8.863335E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="R58" s="73">
         <v>8.863335E-3</v>
       </c>
       <c r="S58" s="73">
-        <v>8.4573138699999995E-2</v>
+        <v>17033.331630000001</v>
       </c>
       <c r="T58" s="73">
-        <v>3.7296719499999999E-2</v>
+        <v>11355.55442</v>
       </c>
       <c r="U58" s="73">
         <v>0</v>
       </c>
       <c r="V58" s="73">
-        <v>6.7150979999999999E-4</v>
+        <v>18459.998154000001</v>
       </c>
       <c r="W58" s="73">
-        <v>1.1346769200000001E-2</v>
+        <v>8516.6658150000003</v>
       </c>
       <c r="X58" s="73">
-        <v>0.63879087099999998</v>
+        <v>3244.4441200000001</v>
       </c>
       <c r="Y58" s="73">
-        <v>0.33091316500000001</v>
+        <v>3244.4441200000001</v>
       </c>
       <c r="Z58" s="73">
-        <v>3.8841001600000001E-2</v>
+        <v>14194.443025</v>
       </c>
       <c r="AA58" s="73">
-        <v>0.71459090199999997</v>
+        <v>12977.77648</v>
       </c>
       <c r="AB58" s="73">
-        <v>1.3850370022</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AC58" s="73">
-        <v>1.8770639000000001E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AD58" s="73">
-        <v>2.44532568E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AE58" s="73">
-        <v>1.1461828504</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AF58" s="73">
         <v>4.4145742501000003</v>
@@ -6361,91 +6361,91 @@
         <v>52</v>
       </c>
       <c r="C59" s="73">
-        <v>0.50574823530049995</v>
+        <v>17033.331630000001</v>
       </c>
       <c r="D59" s="73">
-        <v>0.45265177836129999</v>
+        <v>11355.55442</v>
       </c>
       <c r="E59" s="73">
         <v>0</v>
       </c>
       <c r="F59" s="73">
-        <v>0.44315559400479998</v>
+        <v>17033.331630000001</v>
       </c>
       <c r="G59" s="73">
-        <v>0.21914233301790001</v>
+        <v>8516.6658150000003</v>
       </c>
       <c r="H59" s="73">
-        <v>0.18657599999819999</v>
+        <v>23426.664324000001</v>
       </c>
       <c r="I59" s="73">
-        <v>16.1513144</v>
+        <v>12977.77648</v>
       </c>
       <c r="J59" s="73">
-        <v>2.6806080600006998</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="K59" s="73">
-        <v>0.27796587775429998</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="L59" s="73">
-        <v>2.1216535837600001E-2</v>
+        <v>2659.999734</v>
       </c>
       <c r="M59" s="73">
-        <v>0.7276961999996</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="N59" s="73">
-        <v>5.9716879419600001E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="O59" s="73">
-        <v>5.25066799998E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="P59" s="73">
         <v>21.7782985736943</v>
       </c>
       <c r="Q59" s="73">
-        <v>7.2553500005999999E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="R59" s="73">
         <v>7.2553500005999999E-3</v>
       </c>
       <c r="S59" s="73">
-        <v>9.9531064099999997E-2</v>
+        <v>17033.331630000001</v>
       </c>
       <c r="T59" s="73">
-        <v>3.11744724E-2</v>
+        <v>11355.55442</v>
       </c>
       <c r="U59" s="73">
         <v>0</v>
       </c>
       <c r="V59" s="73">
-        <v>9.4640429999999997E-4</v>
+        <v>17033.331630000001</v>
       </c>
       <c r="W59" s="73">
-        <v>6.9766825999999999E-3</v>
+        <v>8516.6658150000003</v>
       </c>
       <c r="X59" s="73">
-        <v>0.61933886699999996</v>
+        <v>3244.4441200000001</v>
       </c>
       <c r="Y59" s="73">
-        <v>0.27731972399999999</v>
+        <v>3244.4441200000001</v>
       </c>
       <c r="Z59" s="73">
-        <v>0.1002750027</v>
+        <v>14194.443025</v>
       </c>
       <c r="AA59" s="73">
-        <v>0.70981551099999995</v>
+        <v>12977.77648</v>
       </c>
       <c r="AB59" s="73">
-        <v>1.4684396805</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AC59" s="73">
-        <v>4.8819468000000001E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AD59" s="73">
-        <v>8.5768153999999999E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AE59" s="73">
-        <v>0.53936415029999996</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AF59" s="73">
         <v>3.8666403211000002</v>
@@ -6460,91 +6460,91 @@
         <v>53</v>
       </c>
       <c r="C60" s="73">
-        <v>0.45862536142479998</v>
+        <v>14793.331854</v>
       </c>
       <c r="D60" s="73">
-        <v>0.34662770991050001</v>
+        <v>11355.55442</v>
       </c>
       <c r="E60" s="73">
         <v>0</v>
       </c>
       <c r="F60" s="73">
-        <v>0.65409551200600002</v>
+        <v>22361.108875000002</v>
       </c>
       <c r="G60" s="73">
-        <v>7.7207052510299995E-2</v>
+        <v>3141.1107969999998</v>
       </c>
       <c r="H60" s="73">
-        <v>0.1691660000039</v>
+        <v>25549.997445000001</v>
       </c>
       <c r="I60" s="73">
-        <v>0.80556346419680003</v>
+        <v>10639.998936</v>
       </c>
       <c r="J60" s="73">
-        <v>2.4631687600003001</v>
+        <v>2706.6663960000001</v>
       </c>
       <c r="K60" s="73">
-        <v>0.2437548475047</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="L60" s="73">
-        <v>5.7699969975000001E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="M60" s="73">
-        <v>1.1035464041530001</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="N60" s="73">
-        <v>5.7970123530500003E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="O60" s="73">
-        <v>5.2864919999899999E-2</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="P60" s="73">
         <v>6.4902901252156999</v>
       </c>
       <c r="Q60" s="73">
-        <v>5.2960500004000004E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="R60" s="73">
         <v>5.2960500004000004E-3</v>
       </c>
       <c r="S60" s="73">
-        <v>7.9138956499999996E-2</v>
+        <v>16193.331714</v>
       </c>
       <c r="T60" s="73">
-        <v>2.1863520300000001E-2</v>
+        <v>11355.55442</v>
       </c>
       <c r="U60" s="73">
         <v>0</v>
       </c>
       <c r="V60" s="73">
-        <v>1.6170035000000001E-3</v>
+        <v>22469.997753</v>
       </c>
       <c r="W60" s="73">
-        <v>2.3245111000000001E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="X60" s="73">
-        <v>0.7185337222</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="Y60" s="73">
-        <v>0.2330015953</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="Z60" s="73">
-        <v>0.117705005</v>
+        <v>14194.443025</v>
       </c>
       <c r="AA60" s="73">
-        <v>0.61024679800000003</v>
+        <v>10639.998936</v>
       </c>
       <c r="AB60" s="73">
-        <v>1.1435139132000001</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AC60" s="73">
-        <v>6.6903683999999996E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AD60" s="73">
-        <v>8.1769977000000008E-3</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AE60" s="73">
-        <v>0.68836905120000003</v>
+        <v>2838.8886050000001</v>
       </c>
       <c r="AF60" s="73">
         <v>3.6311814424</v>
@@ -6559,91 +6559,91 @@
         <v>54</v>
       </c>
       <c r="C61" s="73">
-        <v>0.4</v>
+        <v>399.99995999999999</v>
       </c>
       <c r="D61" s="73">
-        <v>0.39</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="E61" s="73">
         <v>0</v>
       </c>
       <c r="F61" s="73">
-        <v>0.66062318900000006</v>
+        <v>664.44437800000003</v>
       </c>
       <c r="G61" s="73">
-        <v>8.5999999999999993E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="H61" s="73">
-        <v>0.124</v>
+        <v>599.99994000000004</v>
       </c>
       <c r="I61" s="73">
-        <v>1.6839999999999999</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="J61" s="73">
-        <v>2.3170000000000002</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="K61" s="73">
-        <v>0.58299999999999996</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="L61" s="73">
-        <v>7.5999999999999998E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="M61" s="73">
-        <v>0.72399999999999998</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="N61" s="73">
-        <v>5.6000000000000001E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="O61" s="73">
-        <v>7.4999999999999997E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="P61" s="73">
         <v>7.1756231890000004</v>
       </c>
       <c r="Q61" s="73">
-        <v>3.0000000000000001E-3</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="R61" s="73">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="S61" s="73">
-        <v>8.2000000000000003E-2</v>
+        <v>399.99995999999999</v>
       </c>
       <c r="T61" s="73">
-        <v>2.9000000000000001E-2</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="U61" s="73">
         <v>0</v>
       </c>
       <c r="V61" s="73">
-        <v>1E-3</v>
+        <v>566.66660999999999</v>
       </c>
       <c r="W61" s="73">
-        <v>3.0000000000000001E-3</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="X61" s="73">
-        <v>0.65500000000000003</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="Y61" s="73">
-        <v>0.17799999999999999</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="Z61" s="73">
-        <v>0.114</v>
+        <v>333.33330000000001</v>
       </c>
       <c r="AA61" s="73">
-        <v>0.70099999999999996</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="AB61" s="73">
-        <v>1.1379999999999999</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AC61" s="73">
-        <v>8.0000000000000002E-3</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AD61" s="73">
-        <v>1.2999999999999999E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AE61" s="73">
-        <v>0.41799999999999998</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AF61" s="73">
         <v>3.34</v>
@@ -6658,91 +6658,91 @@
         <v>55</v>
       </c>
       <c r="C62" s="73">
-        <v>0.48699999999999999</v>
+        <v>466.66662000000002</v>
       </c>
       <c r="D62" s="73">
-        <v>0.36599999999999999</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="E62" s="73">
         <v>0</v>
       </c>
       <c r="F62" s="73">
-        <v>0.82799999999999996</v>
+        <v>555.55550000000005</v>
       </c>
       <c r="G62" s="73">
-        <v>0.112</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="H62" s="73">
-        <v>0.105</v>
+        <v>599.99994000000004</v>
       </c>
       <c r="I62" s="73">
-        <v>1.4830000000000001</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="J62" s="73">
-        <v>2.2040000000000002</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="K62" s="73">
-        <v>0.63</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="L62" s="73">
-        <v>0.14699999999999999</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="M62" s="73">
-        <v>0.76</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="N62" s="73">
-        <v>4.8000000000000001E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="O62" s="73">
-        <v>9.2999999999999999E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="P62" s="73">
         <v>7.2629999999999999</v>
       </c>
       <c r="Q62" s="73">
-        <v>2E-3</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="R62" s="73">
         <v>2E-3</v>
       </c>
       <c r="S62" s="73">
-        <v>0.11600000000000001</v>
+        <v>466.66662000000002</v>
       </c>
       <c r="T62" s="73">
-        <v>2.7E-2</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="U62" s="73">
         <v>0</v>
       </c>
       <c r="V62" s="73">
-        <v>1E-3</v>
+        <v>555.55550000000005</v>
       </c>
       <c r="W62" s="73">
-        <v>4.0000000000000001E-3</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="X62" s="73">
-        <v>0.65700000000000003</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="Y62" s="73">
-        <v>0.19500000000000001</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="Z62" s="73">
-        <v>9.2999999999999999E-2</v>
+        <v>333.33330000000001</v>
       </c>
       <c r="AA62" s="73">
-        <v>0.70299999999999996</v>
+        <v>266.66663999999997</v>
       </c>
       <c r="AB62" s="73">
-        <v>1.032</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AC62" s="73">
-        <v>8.9999999999999993E-3</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AD62" s="73">
-        <v>1.7000000000000001E-2</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AE62" s="73">
-        <v>0.159</v>
+        <v>66.666659999999993</v>
       </c>
       <c r="AF62" s="73">
         <v>3.0129999999999999</v>
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16632D9-15DE-4481-9433-21EE3E52B5BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4DB4BF4-8B06-4099-95BA-059E7458CEAE}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{131318A5-280E-439F-9646-C8ACA513D39D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F5D498-5F47-40EB-A46A-609907C38466}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_dummy.xlsx
+++ b/dpr_dummy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D1BAB95-D2DF-44AC-AE85-7A69B029BDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A10BED9-1E1F-4961-B8C9-CE3D1741C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{1AB92B17-2BEC-47DC-8530-EB04EDF03A72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{6130DCD7-03C9-4EBC-A9EE-AA9CFD200924}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 16:42:02</t>
+    <t>Report Generated On: 05.MAY.2026 At 17:00:53</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6C44-49E6-926A-1E99E4AA02FD}"/>
+              <c16:uniqueId val="{00000000-19FF-4141-BD92-60AD0E5CD856}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6C44-49E6-926A-1E99E4AA02FD}"/>
+              <c16:uniqueId val="{00000001-19FF-4141-BD92-60AD0E5CD856}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="172966047"/>
-        <c:axId val="172955007"/>
+        <c:axId val="685954895"/>
+        <c:axId val="685957295"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="172966047"/>
+        <c:axId val="685954895"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="172955007"/>
+        <c:crossAx val="685957295"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="172955007"/>
+        <c:axId val="685957295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="172966047"/>
+        <c:crossAx val="685954895"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1260,16 +1260,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+      <xdr:colOff>663575</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CAF57CF-A70D-9CE7-BBD3-260C39A94A5E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54439D27-141D-87FF-098A-0BBA6FDEED48}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A6FD010-F2F2-33BF-E744-A24D43FC7DF7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{890FCB4C-27DD-75BF-8E2A-9F6319BED5E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0BD5CC-5A6E-4066-8157-6C7D7DB3F6A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B8176-39D2-4BBB-95F4-6276CB8018EA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6262,97 +6262,97 @@
         <v>51</v>
       </c>
       <c r="C58" s="73">
-        <v>17033.331630000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="D58" s="73">
-        <v>11355.55442</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="E58" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="F58" s="73">
-        <v>18459.998154000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="G58" s="73">
-        <v>8516.6658150000003</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="H58" s="73">
-        <v>22711.108840000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="I58" s="73">
-        <v>12977.77648</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="J58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="K58" s="73">
-        <v>3176.6663490000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="L58" s="73">
-        <v>3244.4441200000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="M58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="N58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="O58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="P58" s="73">
-        <v>25.114539355448802</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Q58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="R58" s="73">
-        <v>8.863335E-3</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="S58" s="73">
-        <v>17033.331630000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="T58" s="73">
-        <v>11355.55442</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="U58" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="V58" s="73">
-        <v>18459.998154000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="W58" s="73">
-        <v>8516.6658150000003</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="X58" s="73">
-        <v>3244.4441200000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Y58" s="73">
-        <v>3244.4441200000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Z58" s="73">
-        <v>14194.443025</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AA58" s="73">
-        <v>12977.77648</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AB58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AC58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AD58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AE58" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AF58" s="73">
-        <v>4.4145742501000003</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AG58" s="73">
-        <v>29.537976940548798</v>
+        <v>4.4444439999999998</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -6361,97 +6361,97 @@
         <v>52</v>
       </c>
       <c r="C59" s="73">
-        <v>17033.331630000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="D59" s="73">
-        <v>11355.55442</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="E59" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="F59" s="73">
-        <v>17033.331630000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="G59" s="73">
-        <v>8516.6658150000003</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="H59" s="73">
-        <v>23426.664324000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="I59" s="73">
-        <v>12977.77648</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="J59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="K59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="L59" s="73">
-        <v>2659.999734</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="M59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="N59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="O59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="P59" s="73">
-        <v>21.7782985736943</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Q59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="R59" s="73">
-        <v>7.2553500005999999E-3</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="S59" s="73">
-        <v>17033.331630000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="T59" s="73">
-        <v>11355.55442</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="U59" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="V59" s="73">
-        <v>17033.331630000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="W59" s="73">
-        <v>8516.6658150000003</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="X59" s="73">
-        <v>3244.4441200000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Y59" s="73">
-        <v>3244.4441200000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Z59" s="73">
-        <v>14194.443025</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AA59" s="73">
-        <v>12977.77648</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AB59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AC59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AD59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AE59" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AF59" s="73">
-        <v>3.8666403211000002</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AG59" s="73">
-        <v>25.652194244794899</v>
+        <v>4.4444439999999998</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
@@ -6460,97 +6460,97 @@
         <v>53</v>
       </c>
       <c r="C60" s="73">
-        <v>14793.331854</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="D60" s="73">
-        <v>11355.55442</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="E60" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="F60" s="73">
-        <v>22361.108875000002</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="G60" s="73">
-        <v>3141.1107969999998</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="H60" s="73">
-        <v>25549.997445000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="I60" s="73">
-        <v>10639.998936</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="J60" s="73">
-        <v>2706.6663960000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="K60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="L60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="M60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="N60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="O60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="P60" s="73">
-        <v>6.4902901252156999</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Q60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="R60" s="73">
-        <v>5.2960500004000004E-3</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="S60" s="73">
-        <v>16193.331714</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="T60" s="73">
-        <v>11355.55442</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="U60" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="V60" s="73">
-        <v>22469.997753</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="W60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="X60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Y60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Z60" s="73">
-        <v>14194.443025</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AA60" s="73">
-        <v>10639.998936</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AB60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AC60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AD60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AE60" s="73">
-        <v>2838.8886050000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AF60" s="73">
-        <v>3.6311814424</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AG60" s="73">
-        <v>10.1267676176161</v>
+        <v>4.4444439999999998</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.35">
@@ -6559,97 +6559,97 @@
         <v>54</v>
       </c>
       <c r="C61" s="73">
-        <v>399.99995999999999</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="D61" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="E61" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="F61" s="73">
-        <v>664.44437800000003</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="G61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="H61" s="73">
-        <v>599.99994000000004</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="I61" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="J61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="K61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="L61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="M61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="N61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="O61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="P61" s="73">
-        <v>7.1756231890000004</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Q61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="R61" s="73">
-        <v>3.0000000000000001E-3</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="S61" s="73">
-        <v>399.99995999999999</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="T61" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="U61" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="V61" s="73">
-        <v>566.66660999999999</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="W61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="X61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Y61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Z61" s="73">
-        <v>333.33330000000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AA61" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AB61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AC61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AD61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AE61" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AF61" s="73">
-        <v>3.34</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AG61" s="73">
-        <v>10.518623188999999</v>
+        <v>4.4444439999999998</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.35">
@@ -6658,97 +6658,97 @@
         <v>55</v>
       </c>
       <c r="C62" s="73">
-        <v>466.66662000000002</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="D62" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="E62" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="F62" s="73">
-        <v>555.55550000000005</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="G62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="H62" s="73">
-        <v>599.99994000000004</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="I62" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="J62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="K62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="L62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="M62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="N62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="O62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="P62" s="73">
-        <v>7.2629999999999999</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Q62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="R62" s="73">
-        <v>2E-3</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="S62" s="73">
-        <v>466.66662000000002</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="T62" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="U62" s="73">
-        <v>0</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="V62" s="73">
-        <v>555.55550000000005</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="W62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="X62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Y62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="Z62" s="73">
-        <v>333.33330000000001</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AA62" s="73">
-        <v>266.66663999999997</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AB62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AC62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AD62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AE62" s="73">
-        <v>66.666659999999993</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AF62" s="73">
-        <v>3.0129999999999999</v>
+        <v>4.4444439999999998</v>
       </c>
       <c r="AG62" s="73">
-        <v>10.278</v>
+        <v>4.4444439999999998</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="17" x14ac:dyDescent="0.4">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4DB4BF4-8B06-4099-95BA-059E7458CEAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3AC64B-7C57-4559-9AA7-1A4C12D39BED}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F5D498-5F47-40EB-A46A-609907C38466}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{250BE1D5-FACE-407A-BF07-34BDE6B35EC0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/dpr_dummy.xlsx
+++ b/dpr_dummy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Client\C$\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A10BED9-1E1F-4961-B8C9-CE3D1741C96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4598D90E-20C5-41A4-BB63-FA0B486C646C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{6130DCD7-03C9-4EBC-A9EE-AA9CFD200924}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{4743B193-21BB-48EC-A048-DB5F99F508D0}"/>
   </bookViews>
   <sheets>
     <sheet name="DPR ( 26-APR-2025 )" sheetId="3" r:id="rId1"/>
@@ -241,7 +241,7 @@
     <t>The respective asset has been relinquished on 31.AUG.2019</t>
   </si>
   <si>
-    <t>Report Generated On: 05.MAY.2026 At 17:00:53</t>
+    <t>Report Generated On: 05.MAY.2026 At 17:14:36</t>
   </si>
   <si>
     <t>Production Date</t>
@@ -1043,7 +1043,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-19FF-4141-BD92-60AD0E5CD856}"/>
+              <c16:uniqueId val="{00000000-067B-43A8-94AE-D28FA8F4D04E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,7 +1156,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-19FF-4141-BD92-60AD0E5CD856}"/>
+              <c16:uniqueId val="{00000001-067B-43A8-94AE-D28FA8F4D04E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1170,11 +1170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="685954895"/>
-        <c:axId val="685957295"/>
+        <c:axId val="1090955983"/>
+        <c:axId val="1090956463"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="685954895"/>
+        <c:axId val="1090955983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1184,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="685957295"/>
+        <c:crossAx val="1090956463"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1192,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="685957295"/>
+        <c:axId val="1090956463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1221,7 +1221,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="685954895"/>
+        <c:crossAx val="1090955983"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1260,16 +1260,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>663575</xdr:colOff>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54439D27-141D-87FF-098A-0BBA6FDEED48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C7D17C-401D-9342-4C13-3927328A91D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1324,7 +1324,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{890FCB4C-27DD-75BF-8E2A-9F6319BED5E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D497661-93C6-FD93-3EC3-E33AA0720DAF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B8176-39D2-4BBB-95F4-6276CB8018EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01858E7-2719-4BC3-A023-22459482AC43}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6262,97 +6262,97 @@
         <v>51</v>
       </c>
       <c r="C58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="D58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="E58" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="F58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="G58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="H58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="I58" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="J58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="K58" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="L58" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="M58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="N58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="O58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="P58" s="73">
-        <v>4.4444439999999998</v>
+        <v>25.114539355448802</v>
       </c>
       <c r="Q58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="R58" s="73">
-        <v>4.4444439999999998</v>
+        <v>8.863335E-3</v>
       </c>
       <c r="S58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="T58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="U58" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="V58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="W58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="X58" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="Y58" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="Z58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AA58" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="AB58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AC58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AD58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AE58" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AF58" s="73">
-        <v>4.4444439999999998</v>
+        <v>4.4145742501000003</v>
       </c>
       <c r="AG58" s="73">
-        <v>4.4444439999999998</v>
+        <v>29.537976940548798</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.35">
@@ -6361,97 +6361,97 @@
         <v>52</v>
       </c>
       <c r="C59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="D59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="E59" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="F59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="G59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="H59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="I59" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="J59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="K59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="L59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="M59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="N59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="O59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="P59" s="73">
-        <v>4.4444439999999998</v>
+        <v>21.7782985736943</v>
       </c>
       <c r="Q59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="R59" s="73">
-        <v>4.4444439999999998</v>
+        <v>7.2553500005999999E-3</v>
       </c>
       <c r="S59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="T59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="U59" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="V59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="W59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="X59" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="Y59" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="Z59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AA59" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.3333330000000001</v>
       </c>
       <c r="AB59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AC59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AD59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AE59" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AF59" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.8666403211000002</v>
       </c>
       <c r="AG59" s="73">
-        <v>4.4444439999999998</v>
+        <v>25.652194244794899</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.35">
@@ -6460,97 +6460,97 @@
         <v>53</v>
       </c>
       <c r="C60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="D60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="E60" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="F60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="G60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="H60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="I60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="J60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="K60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="L60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="M60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="N60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="O60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="P60" s="73">
-        <v>4.4444439999999998</v>
+        <v>6.4902901252156999</v>
       </c>
       <c r="Q60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="R60" s="73">
-        <v>4.4444439999999998</v>
+        <v>5.2960500004000004E-3</v>
       </c>
       <c r="S60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="T60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="U60" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="V60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="W60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="X60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="Y60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="Z60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AA60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AB60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AC60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AD60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AE60" s="73">
-        <v>4.4444439999999998</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="AF60" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.6311814424</v>
       </c>
       <c r="AG60" s="73">
-        <v>4.4444439999999998</v>
+        <v>10.1267676176161</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.35">
@@ -6559,97 +6559,97 @@
         <v>54</v>
       </c>
       <c r="C61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="D61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="E61" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="F61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="G61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="H61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="I61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="J61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="K61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="L61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="M61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="N61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="O61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="P61" s="73">
-        <v>4.4444439999999998</v>
+        <v>7.1756231890000004</v>
       </c>
       <c r="Q61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="R61" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="S61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="T61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="U61" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="V61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="W61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="X61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="Y61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="Z61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AA61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AB61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AC61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AD61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AE61" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AF61" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.34</v>
       </c>
       <c r="AG61" s="73">
-        <v>4.4444439999999998</v>
+        <v>10.518623188999999</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.35">
@@ -6658,97 +6658,97 @@
         <v>55</v>
       </c>
       <c r="C62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="D62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="E62" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="F62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="G62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="H62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="I62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="J62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="K62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="L62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="M62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="N62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="O62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="P62" s="73">
-        <v>4.4444439999999998</v>
+        <v>7.2629999999999999</v>
       </c>
       <c r="Q62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="R62" s="73">
-        <v>4.4444439999999998</v>
+        <v>2E-3</v>
       </c>
       <c r="S62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="T62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="U62" s="73">
-        <v>4.4444439999999998</v>
+        <v>0</v>
       </c>
       <c r="V62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="W62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="X62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="Y62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="Z62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AA62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AB62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AC62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AD62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AE62" s="73">
-        <v>4.4444439999999998</v>
+        <v>1.111111</v>
       </c>
       <c r="AF62" s="73">
-        <v>4.4444439999999998</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="AG62" s="73">
-        <v>4.4444439999999998</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="17" x14ac:dyDescent="0.4">
@@ -6957,7 +6957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3AC64B-7C57-4559-9AA7-1A4C12D39BED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3467C529-82E0-4D04-9592-A84D880D3AE6}">
   <dimension ref="B2:AA4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -7135,7 +7135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{250BE1D5-FACE-407A-BF07-34BDE6B35EC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11FD438F-C542-4A86-803B-2AD88D7D44DB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
